--- a/Unit_Test_Results.xlsx
+++ b/Unit_Test_Results.xlsx
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.2706</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-4.9681</v>
+        <v>-3.8891</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.3599</v>
+        <v>17.3309</v>
       </c>
       <c r="D2" t="n">
         <v>13.4294</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.953</v>
+        <v>1.8813</v>
       </c>
       <c r="D3" t="n">
         <v>2.7055</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.3939</v>
+        <v>21.2348</v>
       </c>
       <c r="D2" t="n">
         <v>13.4294</v>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.3254</v>
+        <v>4.509</v>
       </c>
       <c r="D3" t="n">
         <v>2.7055</v>
